--- a/pwa/videos.xlsx
+++ b/pwa/videos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E15DFD-E898-45A0-A152-9972C5A4BE20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD224FC-48A5-4687-B29E-97735984537D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Métodos de entrenamiento" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ejercicios!$A$1:$C$237</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ejercicios!$A$1:$C$240</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="502">
   <si>
     <t>Categoría</t>
   </si>
@@ -403,16 +403,10 @@
     <t>Empuje y Tracción (Tren superior)</t>
   </si>
   <si>
-    <t>Aperturas</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=wUBdqJUu3fQ</t>
   </si>
   <si>
     <t>Bench press</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=xJressNbxFY&amp;list=UUTr6ksZa-Omw10sOpij44dw&amp;index=70&amp;t=0s</t>
   </si>
   <si>
     <t>BHT</t>
@@ -1519,13 +1513,37 @@
   </si>
   <si>
     <t>Clean and jerk to box step up over head</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=tfZsfpv_Jsk&amp;list=PLQ8-odzRVIMU&amp;index=78</t>
+  </si>
+  <si>
+    <t>Aperturas en banco plano</t>
+  </si>
+  <si>
+    <t>Aperturas en banco inclinado</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3sE2GaxzhBg&amp;list=PLQ8-odzRVIMU&amp;index=77</t>
+  </si>
+  <si>
+    <t>Plyo Cuadrado basico</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VNZSv8kZtqQ&amp;list=PLQ8-odzRVIMU&amp;index=76</t>
+  </si>
+  <si>
+    <t>Pallof press Over head con banda inestable</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=PQCdQfwVah8&amp;list=PLQ8-odzRVIMU&amp;index=75</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1556,6 +1574,14 @@
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -1597,10 +1623,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1614,8 +1641,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1878,7 +1907,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C237"/>
+  <dimension ref="A1:C240"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -2331,10 +2360,10 @@
         <v>47</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>84</v>
+        <v>500</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>85</v>
+        <v>501</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -2342,10 +2371,10 @@
         <v>47</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -2353,10 +2382,10 @@
         <v>47</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>481</v>
+        <v>86</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>480</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2364,10 +2393,10 @@
         <v>47</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>88</v>
+        <v>479</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>89</v>
+        <v>478</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -2375,10 +2404,10 @@
         <v>47</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -2386,10 +2415,10 @@
         <v>47</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -2397,10 +2426,10 @@
         <v>47</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -2408,10 +2437,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -2419,10 +2448,10 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>483</v>
+        <v>96</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>482</v>
+        <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -2430,10 +2459,10 @@
         <v>47</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -2441,10 +2470,10 @@
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>98</v>
+        <v>491</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>99</v>
+        <v>490</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -2452,10 +2481,10 @@
         <v>47</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>491</v>
+        <v>98</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>490</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -2463,10 +2492,10 @@
         <v>47</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>100</v>
+        <v>489</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>101</v>
+        <v>488</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -2474,10 +2503,10 @@
         <v>47</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -2485,10 +2514,10 @@
         <v>47</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -2496,10 +2525,10 @@
         <v>47</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -2507,21 +2536,21 @@
         <v>47</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>110</v>
+        <v>47</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -2529,10 +2558,10 @@
         <v>110</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -2540,10 +2569,10 @@
         <v>110</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -2551,10 +2580,10 @@
         <v>110</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -2562,10 +2591,10 @@
         <v>110</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -2573,21 +2602,21 @@
         <v>110</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -2595,10 +2624,10 @@
         <v>123</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>126</v>
+        <v>495</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -2606,10 +2635,10 @@
         <v>123</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>129</v>
+        <v>496</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -2617,10 +2646,10 @@
         <v>123</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -2628,10 +2657,10 @@
         <v>123</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -2639,10 +2668,10 @@
         <v>123</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -2650,10 +2679,10 @@
         <v>123</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -2661,10 +2690,10 @@
         <v>123</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -2672,10 +2701,10 @@
         <v>123</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -2683,10 +2712,10 @@
         <v>123</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -2694,10 +2723,10 @@
         <v>123</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -2705,10 +2734,10 @@
         <v>123</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -2716,10 +2745,10 @@
         <v>123</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -2727,10 +2756,10 @@
         <v>123</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -2738,10 +2767,10 @@
         <v>123</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -2749,10 +2778,10 @@
         <v>123</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -2760,10 +2789,10 @@
         <v>123</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -2771,10 +2800,10 @@
         <v>123</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -2782,10 +2811,10 @@
         <v>123</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -2793,10 +2822,10 @@
         <v>123</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -2804,10 +2833,10 @@
         <v>123</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -2815,10 +2844,10 @@
         <v>123</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -2826,10 +2855,10 @@
         <v>123</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -2837,10 +2866,10 @@
         <v>123</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -2848,10 +2877,10 @@
         <v>123</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -2859,10 +2888,10 @@
         <v>123</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -2870,10 +2899,10 @@
         <v>123</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -2881,10 +2910,10 @@
         <v>123</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -2892,10 +2921,10 @@
         <v>123</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -2903,10 +2932,10 @@
         <v>123</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -2914,10 +2943,10 @@
         <v>123</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -2925,10 +2954,10 @@
         <v>123</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -2936,10 +2965,10 @@
         <v>123</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -2947,10 +2976,10 @@
         <v>123</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -2958,10 +2987,10 @@
         <v>123</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -2969,10 +2998,10 @@
         <v>123</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -2980,10 +3009,10 @@
         <v>123</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -2991,10 +3020,10 @@
         <v>123</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3002,1499 +3031,1532 @@
         <v>123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>202</v>
+        <v>123</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>202</v>
+        <v>123</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>265</v>
+        <v>200</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>265</v>
+        <v>200</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>270</v>
+        <v>498</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>271</v>
+        <v>499</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C140" s="3" t="s">
         <v>272</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="C140" s="3" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>495</v>
+        <v>277</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>494</v>
+        <v>278</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>289</v>
+        <v>493</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>290</v>
+        <v>492</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>489</v>
+        <v>306</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>488</v>
+        <v>308</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>487</v>
+        <v>310</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>484</v>
+        <v>313</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>318</v>
+        <v>485</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>320</v>
+        <v>484</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>322</v>
+        <v>483</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>323</v>
+        <v>482</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>324</v>
+        <v>270</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>324</v>
+        <v>270</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>324</v>
+        <v>270</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C170" s="3" t="s">
         <v>324</v>
-      </c>
-      <c r="B170" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="C170" s="3" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C174" s="3" t="s">
         <v>333</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="C174" s="3" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>467</v>
+        <v>459</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>465</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C237" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:C240" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -4535,197 +4597,198 @@
     <hyperlink ref="C38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
     <hyperlink ref="C39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
     <hyperlink ref="C40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="C41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="C42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="C44" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="C45" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="C46" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="C47" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="C48" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="C51" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="C53" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="C54" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="C55" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="C56" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="C57" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="C58" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="C59" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="C60" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="C61" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="C62" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="C63" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="C64" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="C65" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="C66" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="C67" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="C68" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="C69" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="C70" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="C71" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="C72" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="C73" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="C74" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="C75" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="C76" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="C77" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="C78" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="C79" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="C80" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="C81" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="C82" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="C83" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="C84" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="C85" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="C86" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="C87" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="C88" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="C89" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="C90" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="C91" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="C92" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="C93" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="C94" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="C95" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="C96" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="C97" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="C98" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="C99" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="C100" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="C101" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="C102" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="C103" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="C104" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="C105" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="C106" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="C107" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="C108" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="C109" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="C110" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="C111" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="C112" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="C113" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="C114" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="C115" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="C116" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="C117" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="C118" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="C119" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="C120" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="C121" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="C122" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="C123" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="C124" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="C125" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="C126" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="C127" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="C128" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="C129" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="C130" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="C131" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="C132" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="C133" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="C134" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="C135" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="C136" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="C137" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="C138" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="C139" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="C140" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="C141" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="C142" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="C144" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="C145" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="C146" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="C147" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="C148" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="C149" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="C150" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="C151" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="C152" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="C153" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="C154" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="C155" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="C156" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="C157" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="C158" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="C159" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="C160" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="C161" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="C162" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="C164" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="C165" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="C166" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="C167" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="C168" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="C169" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="C170" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="C171" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="C172" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="C173" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="C174" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="C175" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="C176" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="C177" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="C178" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="C179" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="C180" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="C181" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="C182" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="C183" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="C184" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="C185" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="C186" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="C187" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="C188" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="C189" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="C190" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="C191" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="C192" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="C193" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="C194" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="C195" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="C196" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="C197" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="C198" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="C199" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="C200" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="C201" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="C202" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="C203" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="C204" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="C205" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="C206" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="C207" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="C208" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="C209" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="C210" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="C211" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="C212" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="C213" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="C214" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="C215" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
-    <hyperlink ref="C216" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
-    <hyperlink ref="C217" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="C218" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="C219" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="C220" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="C221" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="C222" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="C223" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="C224" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="C225" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
-    <hyperlink ref="C226" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="C227" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="C228" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="C229" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="C230" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="C231" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="C232" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="C233" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="C234" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="C235" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="C236" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="C237" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="C42" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="C43" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="C45" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="C46" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="C47" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="C48" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="C49" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="C52" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="C54" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="C55" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="C56" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="C57" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="C58" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="C59" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="C60" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="C61" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="C62" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="C63" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="C64" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="C65" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="C68" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="C69" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="C70" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="C71" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="C72" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="C73" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="C74" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="C75" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="C76" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="C77" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="C78" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="C79" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="C80" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="C81" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="C82" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="C83" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="C84" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="C85" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="C86" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="C87" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="C88" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="C89" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="C90" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="C91" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="C92" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="C93" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="C94" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="C95" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="C96" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="C97" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="C98" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="C99" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="C100" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="C101" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="C102" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="C103" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="C104" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="C105" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="C106" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="C107" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="C108" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="C109" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="C110" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="C111" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="C112" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="C113" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="C114" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="C115" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="C116" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="C117" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="C118" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="C119" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="C120" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="C121" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="C122" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="C123" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="C124" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="C125" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="C126" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="C127" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="C128" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="C129" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="C130" r:id="rId122" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="C131" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="C132" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="C133" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="C134" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="C135" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="C137" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="C138" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="C139" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="C140" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="C141" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="C142" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="C143" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="C144" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="C145" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="C147" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="C148" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="C149" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="C150" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="C151" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="C152" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="C153" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="C154" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="C155" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="C156" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="C157" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="C158" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="C159" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="C160" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="C161" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="C162" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="C163" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="C164" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="C165" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="C167" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="C168" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="C169" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="C170" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="C171" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="C172" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="C173" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="C174" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="C175" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="C176" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="C177" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="C178" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="C179" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="C180" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="C181" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="C182" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="C183" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="C184" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="C185" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="C186" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="C187" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="C188" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="C189" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="C190" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="C191" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="C192" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="C193" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="C194" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="C195" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="C196" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="C197" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="C198" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="C199" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="C200" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="C201" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="C202" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="C203" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="C204" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="C205" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="C206" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="C207" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="C208" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="C209" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="C210" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="C211" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="C212" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="C213" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="C214" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="C215" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="C216" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="C217" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="C218" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="C219" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="C220" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="C221" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="C222" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="C223" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="C224" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="C225" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="C226" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="C227" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="C228" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="C229" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
+    <hyperlink ref="C230" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="C231" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="C232" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="C233" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="C234" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="C235" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="C236" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="C237" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="C238" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="C239" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="C240" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="C67" r:id="rId230" xr:uid="{EEF418B1-C72B-4A5A-86A4-FB1098479A15}"/>
+    <hyperlink ref="C66" r:id="rId231" xr:uid="{B5C36226-6E7C-423B-87AF-8866E401D6E0}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4743,50 +4806,50 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>
